--- a/MP变动记录.xlsx
+++ b/MP变动记录.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K356"/>
+  <dimension ref="A1:K362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14248,32 +14248,32 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -14283,52 +14283,52 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/11/16</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>-29</v>
+        <v>171</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/09/20 16:40:56</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Raider A16 HX B9WI</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -14338,75 +14338,75 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/11/16</t>
         </is>
       </c>
       <c r="I254" t="n">
-        <v>-29</v>
+        <v>171</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無.</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/09/20 16:40:56</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Raider A16 HX B9WJ</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/11/16</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無.</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/09/20 16:40:56</t>
         </is>
       </c>
     </row>
@@ -14418,12 +14418,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -14438,21 +14438,21 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I256" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -14473,17 +14473,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14493,21 +14493,21 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I257" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14548,25 +14548,25 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -14583,17 +14583,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -14603,25 +14603,25 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>-20</v>
+        <v>59</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -14638,12 +14638,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -14658,21 +14658,21 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I260" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -14713,25 +14713,25 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -14748,17 +14748,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14768,25 +14768,25 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -14828,16 +14828,16 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I263" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14878,12 +14878,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -14892,7 +14892,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -14913,17 +14913,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -14933,21 +14933,21 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I265" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -14968,17 +14968,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -14998,11 +14998,11 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I266" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -15023,12 +15023,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -15043,21 +15043,21 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I267" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -15078,17 +15078,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15098,21 +15098,21 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I268" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15153,25 +15153,25 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -15188,17 +15188,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15208,25 +15208,25 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I270" t="n">
-        <v>-20</v>
+        <v>59</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -15243,12 +15243,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -15263,21 +15263,21 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I271" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15318,25 +15318,25 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I272" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -15353,17 +15353,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15373,25 +15373,25 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I273" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -15408,12 +15408,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -15433,16 +15433,16 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I274" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15483,12 +15483,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -15497,7 +15497,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -15518,17 +15518,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -15538,21 +15538,21 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -15573,17 +15573,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -15603,11 +15603,11 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -15628,12 +15628,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -15648,21 +15648,21 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I278" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -15683,17 +15683,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -15703,21 +15703,21 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I279" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -15758,25 +15758,25 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -15793,17 +15793,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -15813,25 +15813,25 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I281" t="n">
-        <v>-20</v>
+        <v>59</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -15848,12 +15848,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -15868,21 +15868,21 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -15923,25 +15923,25 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I283" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -15958,17 +15958,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -15978,25 +15978,25 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I284" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -16038,16 +16038,16 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I285" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -16102,7 +16102,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -16123,17 +16123,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -16143,21 +16143,21 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I287" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -16178,17 +16178,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -16208,11 +16208,11 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I288" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -16253,21 +16253,21 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I289" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -16288,17 +16288,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -16308,21 +16308,21 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I290" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16363,25 +16363,25 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I291" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -16398,17 +16398,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16418,25 +16418,25 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I292" t="n">
-        <v>-20</v>
+        <v>59</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -16453,12 +16453,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -16473,21 +16473,21 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I293" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16528,25 +16528,25 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I294" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -16563,17 +16563,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16583,25 +16583,25 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I295" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -16618,12 +16618,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -16643,16 +16643,16 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I296" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -16693,12 +16693,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -16728,17 +16728,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -16748,21 +16748,21 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I298" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -16783,17 +16783,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -16813,11 +16813,11 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -16838,12 +16838,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -16858,21 +16858,21 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I300" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -16893,17 +16893,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16913,21 +16913,21 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16968,25 +16968,25 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I302" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -17003,17 +17003,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17023,25 +17023,25 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I303" t="n">
-        <v>-20</v>
+        <v>59</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -17058,12 +17058,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -17078,21 +17078,21 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I304" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17133,25 +17133,25 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I305" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -17168,17 +17168,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17188,25 +17188,25 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I306" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -17223,12 +17223,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -17248,16 +17248,16 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I307" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17298,12 +17298,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -17333,17 +17333,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17353,21 +17353,21 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I309" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -17388,17 +17388,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -17418,11 +17418,11 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I310" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -17443,12 +17443,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -17463,21 +17463,21 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I311" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -17498,17 +17498,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17518,21 +17518,21 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I312" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17573,25 +17573,25 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I313" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -17628,25 +17628,25 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I314" t="n">
-        <v>-20</v>
+        <v>59</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -17663,12 +17663,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -17683,21 +17683,21 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I315" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -17738,25 +17738,25 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I316" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -17773,17 +17773,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17793,25 +17793,25 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I317" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -17828,12 +17828,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -17853,16 +17853,16 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I318" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -17883,17 +17883,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -17908,16 +17908,16 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I319" t="n">
-        <v>-28</v>
+        <v>-67</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -17938,17 +17938,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -17958,21 +17958,21 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I320" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -17993,12 +17993,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -18027,7 +18027,7 @@
         </is>
       </c>
       <c r="I321" t="n">
-        <v>-28</v>
+        <v>59</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -18048,17 +18048,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18068,21 +18068,21 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I322" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -18158,17 +18158,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18178,21 +18178,21 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I324" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -18213,17 +18213,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -18238,16 +18238,16 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I325" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -18268,17 +18268,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18293,20 +18293,20 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I326" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -18323,17 +18323,17 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -18348,16 +18348,16 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I327" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -18378,12 +18378,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -18403,16 +18403,16 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I328" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -18433,12 +18433,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -18458,25 +18458,25 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I329" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18498,7 +18498,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -18543,17 +18543,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18568,20 +18568,20 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I331" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -18598,17 +18598,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -18623,16 +18623,16 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I332" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -18653,12 +18653,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -18678,16 +18678,16 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I333" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -18708,12 +18708,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -18733,25 +18733,25 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I334" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -18818,17 +18818,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -18843,20 +18843,20 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I336" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -18873,17 +18873,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -18898,16 +18898,16 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I337" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -18953,12 +18953,12 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I338" t="n">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -19008,12 +19008,12 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I339" t="n">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -19063,12 +19063,12 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I340" t="n">
@@ -19081,34 +19081,34 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>26V1</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Modern 16 LE J3M</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -19118,52 +19118,52 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I341" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>1)Schedule: 8/7通知微步八月份680台訂單先備舊料, TTM Schedule由原定的8/26更新至9/7 ready, Delay 10 days. 2) function issue: 同24V1 3) 八&amp;九月訂單認證追蹤(total 2970 pcs）：a.DE* 1650 CE認證, 取證時間target 8/25 b.IT *300 CE認證, 取證時間target 8/25 c.US *1020 FCC ID， Target 9/M取證(等Intel回簽授權文件)</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>2026/08/14 13:19:05</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -19173,52 +19173,52 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I342" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -19228,52 +19228,52 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I343" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -19283,52 +19283,52 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/12/16</t>
         </is>
       </c>
       <c r="I344" t="n">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/09/20 16:40:56</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -19338,52 +19338,52 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/12/16</t>
         </is>
       </c>
       <c r="I345" t="n">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/09/20 16:40:56</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX E9WGXK</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -19393,52 +19393,52 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/12/16</t>
         </is>
       </c>
       <c r="I346" t="n">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/09/20 16:40:56</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>26V1</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Modern 16 LE J3M</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>WCL 25W</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -19448,25 +19448,25 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="I347" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1)Schedule: 8/7通知微步八月份680台訂單先備舊料, TTM Schedule由原定的8/26更新至9/7 ready, Delay 10 days. 2) function issue: 同24V1 3) 八&amp;九月訂單認證追蹤(total 2970 pcs）：a.DE* 1650 CE認證, 取證時間target 8/25 b.IT *300 CE認證, 取證時間target 8/25 c.US *1020 FCC ID， Target 9/M取證(等Intel回簽授權文件)</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/08/14 13:19:05</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19521,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -19736,12 +19736,12 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -19791,12 +19791,12 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -19846,12 +19846,12 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -19888,25 +19888,25 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>2026/07/13</t>
-        </is>
-      </c>
       <c r="I355" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -19923,43 +19923,373 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I356" t="n">
+        <v>13</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>2026/05/28 15:30:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I357" t="n">
+        <v>13</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>2026/05/28 15:36:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I358" t="n">
+        <v>13</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I359" t="n">
+        <v>13</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I360" t="n">
+        <v>13</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="I361" t="n">
+        <v>5</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>2026/06/26 13:22:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
           <t>RMB 100 28W</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="D362" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
+      <c r="E362" t="inlineStr">
         <is>
           <t>杜晨光</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
+      <c r="F362" t="inlineStr">
         <is>
           <t>ATS</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
+      <c r="G362" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
+      <c r="H362" t="inlineStr">
         <is>
           <t>2026/07/20</t>
         </is>
       </c>
-      <c r="I356" t="n">
+      <c r="I362" t="n">
         <v>5</v>
       </c>
-      <c r="J356" t="inlineStr">
+      <c r="J362" t="inlineStr">
         <is>
           <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
+      <c r="K362" t="inlineStr">
         <is>
           <t>2026/07/16 14:20:24</t>
         </is>
